--- a/Template Sensory Score Calculator.xlsx
+++ b/Template Sensory Score Calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fy7078/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fy7078/Desktop/JOVE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CDA2A13-492B-7E41-B617-A9AF48C501A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C942CD2E-816E-514D-B004-C3EAC23CDC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="18000" xr2:uid="{AAA32852-9C90-954A-ABCC-4DA724CC84D0}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{AAA32852-9C90-954A-ABCC-4DA724CC84D0}"/>
   </bookViews>
   <sheets>
     <sheet name="SIGE Calculator" sheetId="1" r:id="rId1"/>
@@ -522,19 +522,19 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D2" t="e">
-        <f>7.11/C2</f>
+        <f>6.096/C2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F2" t="e">
-        <f>7.11/E2</f>
+        <f>6.096/E2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H2" t="e">
-        <f>6.86/G2</f>
+        <f>6.096/G2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J2" t="e">
-        <f>6.86/I2</f>
+        <f>6.096/I2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L2" t="e">
@@ -552,19 +552,19 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D3" t="e">
-        <f t="shared" ref="D3:D44" si="0">7.11/C3</f>
+        <f t="shared" ref="D3:D43" si="0">6.096/C3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F3" t="e">
-        <f t="shared" ref="F3:F44" si="1">7.11/E3</f>
+        <f t="shared" ref="F3:F44" si="1">6.096/E3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H3" t="e">
-        <f t="shared" ref="H3:H44" si="2">6.86/G3</f>
+        <f t="shared" ref="H3:H44" si="2">6.096/G3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J3" t="e">
-        <f t="shared" ref="J3:J44" si="3">6.86/I3</f>
+        <f t="shared" ref="J3:J44" si="3">6.096/I3</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L3" t="e">
@@ -1796,7 +1796,7 @@
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="D44" t="e">
-        <f t="shared" si="0"/>
+        <f>6.096/C44</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F44" t="e">
